--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483843</v>
+        <v>123483640</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461305</v>
+        <v>461380</v>
       </c>
       <c r="R2" t="n">
-        <v>6717564</v>
+        <v>6717576</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483916</v>
+        <v>123483850</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>95669</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +793,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461192</v>
+        <v>461289</v>
       </c>
       <c r="R3" t="n">
-        <v>6717590</v>
+        <v>6717597</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483640</v>
+        <v>123483735</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461380</v>
+        <v>461338</v>
       </c>
       <c r="R4" t="n">
-        <v>6717576</v>
+        <v>6717621</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483933</v>
+        <v>123483907</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461186</v>
+        <v>461180</v>
       </c>
       <c r="R5" t="n">
-        <v>6717575</v>
+        <v>6717581</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1108,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483907</v>
+        <v>123483933</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461180</v>
+        <v>461186</v>
       </c>
       <c r="R6" t="n">
-        <v>6717581</v>
+        <v>6717575</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1214,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483602</v>
+        <v>123483693</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461381</v>
+        <v>461349</v>
       </c>
       <c r="R7" t="n">
-        <v>6717608</v>
+        <v>6717595</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483850</v>
+        <v>123483817</v>
       </c>
       <c r="B8" t="n">
-        <v>95663</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,28 +1324,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1364,13 +1360,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461289</v>
+        <v>461318</v>
       </c>
       <c r="R8" t="n">
-        <v>6717597</v>
+        <v>6717563</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483794</v>
+        <v>123483701</v>
       </c>
       <c r="B9" t="n">
-        <v>95663</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,31 +1435,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1471,13 +1466,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461357</v>
+        <v>461349</v>
       </c>
       <c r="R9" t="n">
-        <v>6717536</v>
+        <v>6717583</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483888</v>
+        <v>123483916</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,39 +1541,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1586,13 +1572,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461180</v>
+        <v>461192</v>
       </c>
       <c r="R10" t="n">
-        <v>6717538</v>
+        <v>6717590</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483726</v>
+        <v>123483794</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>95669</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,30 +1647,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1692,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461329</v>
+        <v>461357</v>
       </c>
       <c r="R11" t="n">
-        <v>6717642</v>
+        <v>6717536</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1755,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483679</v>
+        <v>123483898</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,30 +1754,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1798,13 +1794,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461365</v>
+        <v>461163</v>
       </c>
       <c r="R12" t="n">
-        <v>6717606</v>
+        <v>6717595</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483865</v>
+        <v>123483726</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,39 +1869,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461215</v>
+        <v>461329</v>
       </c>
       <c r="R13" t="n">
-        <v>6717569</v>
+        <v>6717642</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1976,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483817</v>
+        <v>123483670</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,35 +1975,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2024,13 +2006,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461318</v>
+        <v>461373</v>
       </c>
       <c r="R14" t="n">
-        <v>6717563</v>
+        <v>6717597</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483657</v>
+        <v>123483942</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,13 +2112,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461361</v>
+        <v>461218</v>
       </c>
       <c r="R15" t="n">
-        <v>6717583</v>
+        <v>6717602</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483898</v>
+        <v>123483730</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,39 +2187,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2245,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461163</v>
+        <v>461321</v>
       </c>
       <c r="R16" t="n">
-        <v>6717595</v>
+        <v>6717630</v>
       </c>
       <c r="S16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,7 +2284,7 @@
         <v>123483953</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483735</v>
+        <v>123483679</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2457,13 +2430,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461338</v>
+        <v>461365</v>
       </c>
       <c r="R18" t="n">
-        <v>6717621</v>
+        <v>6717606</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2520,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483701</v>
+        <v>123483888</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,30 +2505,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2563,13 +2545,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461349</v>
+        <v>461180</v>
       </c>
       <c r="R19" t="n">
-        <v>6717583</v>
+        <v>6717538</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483670</v>
+        <v>123483762</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>95669</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2638,30 +2620,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,13 +2652,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461373</v>
+        <v>461360</v>
       </c>
       <c r="R20" t="n">
-        <v>6717597</v>
+        <v>6717558</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483762</v>
+        <v>123483602</v>
       </c>
       <c r="B21" t="n">
-        <v>95663</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2744,31 +2727,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2776,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461360</v>
+        <v>461381</v>
       </c>
       <c r="R21" t="n">
-        <v>6717558</v>
+        <v>6717608</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,10 +2821,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483730</v>
+        <v>123483657</v>
       </c>
       <c r="B22" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2882,13 +2864,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461321</v>
+        <v>461361</v>
       </c>
       <c r="R22" t="n">
-        <v>6717630</v>
+        <v>6717583</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2945,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483963</v>
+        <v>123483843</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,30 +2939,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2988,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461225</v>
+        <v>461305</v>
       </c>
       <c r="R23" t="n">
-        <v>6717644</v>
+        <v>6717564</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3051,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483942</v>
+        <v>123483686</v>
       </c>
       <c r="B24" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3094,13 +3085,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461218</v>
+        <v>461374</v>
       </c>
       <c r="R24" t="n">
-        <v>6717602</v>
+        <v>6717611</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483686</v>
+        <v>123483963</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461374</v>
+        <v>461225</v>
       </c>
       <c r="R25" t="n">
-        <v>6717611</v>
+        <v>6717644</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483693</v>
+        <v>123483865</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,30 +3266,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461349</v>
+        <v>461215</v>
       </c>
       <c r="R26" t="n">
-        <v>6717595</v>
+        <v>6717569</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483640</v>
+        <v>123483701</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461380</v>
+        <v>461349</v>
       </c>
       <c r="R2" t="n">
-        <v>6717576</v>
+        <v>6717583</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483850</v>
+        <v>123483640</v>
       </c>
       <c r="B3" t="n">
-        <v>95669</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461289</v>
+        <v>461380</v>
       </c>
       <c r="R3" t="n">
-        <v>6717597</v>
+        <v>6717576</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483735</v>
+        <v>123483693</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,13 +930,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461338</v>
+        <v>461349</v>
       </c>
       <c r="R4" t="n">
-        <v>6717621</v>
+        <v>6717595</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483907</v>
+        <v>123483762</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>95672</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,30 +1005,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461180</v>
+        <v>461360</v>
       </c>
       <c r="R5" t="n">
-        <v>6717581</v>
+        <v>6717558</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483933</v>
+        <v>123483888</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,30 +1112,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,13 +1152,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461186</v>
+        <v>461180</v>
       </c>
       <c r="R6" t="n">
-        <v>6717575</v>
+        <v>6717538</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483693</v>
+        <v>123483942</v>
       </c>
       <c r="B7" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,13 +1258,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461349</v>
+        <v>461218</v>
       </c>
       <c r="R7" t="n">
-        <v>6717595</v>
+        <v>6717602</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483817</v>
+        <v>123483602</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,35 +1333,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1360,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461318</v>
+        <v>461381</v>
       </c>
       <c r="R8" t="n">
-        <v>6717563</v>
+        <v>6717608</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483701</v>
+        <v>123483657</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,7 +1470,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461349</v>
+        <v>461361</v>
       </c>
       <c r="R9" t="n">
         <v>6717583</v>
@@ -1529,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483916</v>
+        <v>123483963</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461192</v>
+        <v>461225</v>
       </c>
       <c r="R10" t="n">
-        <v>6717590</v>
+        <v>6717644</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1635,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483794</v>
+        <v>123483817</v>
       </c>
       <c r="B11" t="n">
-        <v>95669</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,28 +1651,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1679,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461357</v>
+        <v>461318</v>
       </c>
       <c r="R11" t="n">
-        <v>6717536</v>
+        <v>6717563</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483898</v>
+        <v>123483843</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,7 +1785,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1794,13 +1802,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461163</v>
+        <v>461305</v>
       </c>
       <c r="R12" t="n">
-        <v>6717595</v>
+        <v>6717564</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483726</v>
+        <v>123483898</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1869,30 +1877,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1900,13 +1917,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461329</v>
+        <v>461163</v>
       </c>
       <c r="R13" t="n">
-        <v>6717642</v>
+        <v>6717595</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483670</v>
+        <v>123483907</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,13 +2023,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461373</v>
+        <v>461180</v>
       </c>
       <c r="R14" t="n">
-        <v>6717597</v>
+        <v>6717581</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483942</v>
+        <v>123483850</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>95672</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,30 +2098,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2112,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461218</v>
+        <v>461289</v>
       </c>
       <c r="R15" t="n">
-        <v>6717602</v>
+        <v>6717597</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2175,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483730</v>
+        <v>123483726</v>
       </c>
       <c r="B16" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2218,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461321</v>
+        <v>461329</v>
       </c>
       <c r="R16" t="n">
-        <v>6717630</v>
+        <v>6717642</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2281,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483953</v>
+        <v>123483916</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461210</v>
+        <v>461192</v>
       </c>
       <c r="R17" t="n">
-        <v>6717613</v>
+        <v>6717590</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2387,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483679</v>
+        <v>123483730</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2430,13 +2448,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461365</v>
+        <v>461321</v>
       </c>
       <c r="R18" t="n">
-        <v>6717606</v>
+        <v>6717630</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2493,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483888</v>
+        <v>123483679</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,39 +2523,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2545,13 +2554,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461180</v>
+        <v>461365</v>
       </c>
       <c r="R19" t="n">
-        <v>6717538</v>
+        <v>6717606</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2608,10 +2617,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483762</v>
+        <v>123483686</v>
       </c>
       <c r="B20" t="n">
-        <v>95669</v>
+        <v>78775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2620,31 +2629,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2652,13 +2660,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461360</v>
+        <v>461374</v>
       </c>
       <c r="R20" t="n">
-        <v>6717558</v>
+        <v>6717611</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2715,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483602</v>
+        <v>123483670</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2758,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461381</v>
+        <v>461373</v>
       </c>
       <c r="R21" t="n">
-        <v>6717608</v>
+        <v>6717597</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2821,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483657</v>
+        <v>123483794</v>
       </c>
       <c r="B22" t="n">
-        <v>78772</v>
+        <v>95672</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2833,30 +2841,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2864,13 +2873,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461361</v>
+        <v>461357</v>
       </c>
       <c r="R22" t="n">
-        <v>6717583</v>
+        <v>6717536</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2927,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483843</v>
+        <v>123483735</v>
       </c>
       <c r="B23" t="n">
-        <v>98376</v>
+        <v>78775</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2939,39 +2948,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461305</v>
+        <v>461338</v>
       </c>
       <c r="R23" t="n">
-        <v>6717564</v>
+        <v>6717621</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483686</v>
+        <v>123483933</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461374</v>
+        <v>461186</v>
       </c>
       <c r="R24" t="n">
-        <v>6717611</v>
+        <v>6717575</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483963</v>
+        <v>123483953</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461225</v>
+        <v>461210</v>
       </c>
       <c r="R25" t="n">
-        <v>6717644</v>
+        <v>6717613</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3257,7 +3257,7 @@
         <v>123483865</v>
       </c>
       <c r="B26" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483762</v>
+        <v>123483942</v>
       </c>
       <c r="B5" t="n">
-        <v>95672</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,31 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461360</v>
+        <v>461218</v>
       </c>
       <c r="R5" t="n">
-        <v>6717558</v>
+        <v>6717602</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1100,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483942</v>
+        <v>123483762</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>95672</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,30 +1111,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461218</v>
+        <v>461360</v>
       </c>
       <c r="R6" t="n">
-        <v>6717602</v>
+        <v>6717558</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483726</v>
+        <v>123483850</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>95672</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,30 +2098,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461329</v>
+        <v>461289</v>
       </c>
       <c r="R15" t="n">
-        <v>6717642</v>
+        <v>6717597</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2192,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483916</v>
+        <v>123483726</v>
       </c>
       <c r="B16" t="n">
         <v>78775</v>
@@ -2235,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461192</v>
+        <v>461329</v>
       </c>
       <c r="R16" t="n">
-        <v>6717590</v>
+        <v>6717642</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2298,7 +2299,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483730</v>
+        <v>123483916</v>
       </c>
       <c r="B17" t="n">
         <v>78775</v>
@@ -2341,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461321</v>
+        <v>461192</v>
       </c>
       <c r="R17" t="n">
-        <v>6717630</v>
+        <v>6717590</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2404,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483850</v>
+        <v>123483730</v>
       </c>
       <c r="B18" t="n">
-        <v>95672</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2416,31 +2417,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461289</v>
+        <v>461321</v>
       </c>
       <c r="R18" t="n">
-        <v>6717597</v>
+        <v>6717630</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483701</v>
+        <v>123483907</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461349</v>
+        <v>461180</v>
       </c>
       <c r="R2" t="n">
-        <v>6717583</v>
+        <v>6717581</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483640</v>
+        <v>123483657</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461380</v>
+        <v>461361</v>
       </c>
       <c r="R3" t="n">
-        <v>6717576</v>
+        <v>6717583</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483693</v>
+        <v>123483640</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461349</v>
+        <v>461380</v>
       </c>
       <c r="R4" t="n">
-        <v>6717595</v>
+        <v>6717576</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483942</v>
+        <v>123483726</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461218</v>
+        <v>461329</v>
       </c>
       <c r="R5" t="n">
-        <v>6717602</v>
+        <v>6717642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483762</v>
+        <v>123483730</v>
       </c>
       <c r="B6" t="n">
-        <v>95672</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,31 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461360</v>
+        <v>461321</v>
       </c>
       <c r="R6" t="n">
-        <v>6717558</v>
+        <v>6717630</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1206,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483888</v>
+        <v>123483850</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>95689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,37 +1217,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1258,13 +1249,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461180</v>
+        <v>461289</v>
       </c>
       <c r="R7" t="n">
-        <v>6717538</v>
+        <v>6717597</v>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483602</v>
+        <v>123483865</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,30 +1324,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461381</v>
+        <v>461215</v>
       </c>
       <c r="R8" t="n">
-        <v>6717608</v>
+        <v>6717569</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483657</v>
+        <v>123483963</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,13 +1470,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461361</v>
+        <v>461225</v>
       </c>
       <c r="R9" t="n">
-        <v>6717583</v>
+        <v>6717644</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483963</v>
+        <v>123483916</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461225</v>
+        <v>461192</v>
       </c>
       <c r="R10" t="n">
-        <v>6717644</v>
+        <v>6717590</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483817</v>
+        <v>123483701</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,35 +1651,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,13 +1682,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461318</v>
+        <v>461349</v>
       </c>
       <c r="R11" t="n">
-        <v>6717563</v>
+        <v>6717583</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483843</v>
+        <v>123483953</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,39 +1757,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1802,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461305</v>
+        <v>461210</v>
       </c>
       <c r="R12" t="n">
-        <v>6717564</v>
+        <v>6717613</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1865,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483898</v>
+        <v>123483843</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1900,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1917,13 +1903,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461163</v>
+        <v>461305</v>
       </c>
       <c r="R13" t="n">
-        <v>6717595</v>
+        <v>6717564</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,10 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483907</v>
+        <v>123483817</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,30 +1978,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461180</v>
+        <v>461318</v>
       </c>
       <c r="R14" t="n">
-        <v>6717581</v>
+        <v>6717563</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483850</v>
+        <v>123483762</v>
       </c>
       <c r="B15" t="n">
-        <v>95672</v>
+        <v>95689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461289</v>
+        <v>461360</v>
       </c>
       <c r="R15" t="n">
-        <v>6717597</v>
+        <v>6717558</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2193,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483726</v>
+        <v>123483794</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>95689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,30 +2196,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2236,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461329</v>
+        <v>461357</v>
       </c>
       <c r="R16" t="n">
-        <v>6717642</v>
+        <v>6717536</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2299,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483916</v>
+        <v>123483686</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,13 +2334,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461192</v>
+        <v>461374</v>
       </c>
       <c r="R17" t="n">
-        <v>6717590</v>
+        <v>6717611</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2405,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483730</v>
+        <v>123483888</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,30 +2409,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,13 +2449,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461321</v>
+        <v>461180</v>
       </c>
       <c r="R18" t="n">
-        <v>6717630</v>
+        <v>6717538</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2511,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483679</v>
+        <v>123483693</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461365</v>
+        <v>461349</v>
       </c>
       <c r="R19" t="n">
-        <v>6717606</v>
+        <v>6717595</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2617,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483686</v>
+        <v>123483942</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2660,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461374</v>
+        <v>461218</v>
       </c>
       <c r="R20" t="n">
-        <v>6717611</v>
+        <v>6717602</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2723,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483670</v>
+        <v>123483602</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461373</v>
+        <v>461381</v>
       </c>
       <c r="R21" t="n">
-        <v>6717597</v>
+        <v>6717608</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2829,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483794</v>
+        <v>123483679</v>
       </c>
       <c r="B22" t="n">
-        <v>95672</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,31 +2842,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461357</v>
+        <v>461365</v>
       </c>
       <c r="R22" t="n">
-        <v>6717536</v>
+        <v>6717606</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483735</v>
+        <v>123483933</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461338</v>
+        <v>461186</v>
       </c>
       <c r="R23" t="n">
-        <v>6717621</v>
+        <v>6717575</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483933</v>
+        <v>123483670</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461186</v>
+        <v>461373</v>
       </c>
       <c r="R24" t="n">
-        <v>6717575</v>
+        <v>6717597</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483953</v>
+        <v>123483898</v>
       </c>
       <c r="B25" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3160,30 +3160,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3191,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461210</v>
+        <v>461163</v>
       </c>
       <c r="R25" t="n">
-        <v>6717613</v>
+        <v>6717595</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483865</v>
+        <v>123483735</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3266,39 +3275,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461215</v>
+        <v>461338</v>
       </c>
       <c r="R26" t="n">
-        <v>6717569</v>
+        <v>6717621</v>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -2618,7 +2618,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483942</v>
+        <v>123483602</v>
       </c>
       <c r="B20" t="n">
         <v>78781</v>
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461218</v>
+        <v>461381</v>
       </c>
       <c r="R20" t="n">
-        <v>6717602</v>
+        <v>6717608</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483602</v>
+        <v>123483942</v>
       </c>
       <c r="B21" t="n">
         <v>78781</v>
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461381</v>
+        <v>461218</v>
       </c>
       <c r="R21" t="n">
-        <v>6717608</v>
+        <v>6717602</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483898</v>
+        <v>123483735</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3160,39 +3160,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3200,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461163</v>
+        <v>461338</v>
       </c>
       <c r="R25" t="n">
-        <v>6717595</v>
+        <v>6717621</v>
       </c>
       <c r="S25" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,10 +3254,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483735</v>
+        <v>123483898</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,30 +3266,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461338</v>
+        <v>461163</v>
       </c>
       <c r="R26" t="n">
-        <v>6717621</v>
+        <v>6717595</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483865</v>
+        <v>123483963</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,39 +1324,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1364,13 +1355,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461215</v>
+        <v>461225</v>
       </c>
       <c r="R8" t="n">
-        <v>6717569</v>
+        <v>6717644</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483963</v>
+        <v>123483916</v>
       </c>
       <c r="B9" t="n">
         <v>78781</v>
@@ -1470,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461225</v>
+        <v>461192</v>
       </c>
       <c r="R9" t="n">
-        <v>6717644</v>
+        <v>6717590</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1533,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483916</v>
+        <v>123483865</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,30 +1536,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461192</v>
+        <v>461215</v>
       </c>
       <c r="R10" t="n">
-        <v>6717590</v>
+        <v>6717569</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483907</v>
+        <v>123483850</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>95695</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461180</v>
+        <v>461289</v>
       </c>
       <c r="R2" t="n">
-        <v>6717581</v>
+        <v>6717597</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483657</v>
+        <v>123483679</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461361</v>
+        <v>461365</v>
       </c>
       <c r="R3" t="n">
-        <v>6717583</v>
+        <v>6717606</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483640</v>
+        <v>123483794</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>95695</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +900,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461380</v>
+        <v>461357</v>
       </c>
       <c r="R4" t="n">
-        <v>6717576</v>
+        <v>6717536</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483726</v>
+        <v>123483602</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461329</v>
+        <v>461381</v>
       </c>
       <c r="R5" t="n">
-        <v>6717642</v>
+        <v>6717608</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483730</v>
+        <v>123483963</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461321</v>
+        <v>461225</v>
       </c>
       <c r="R6" t="n">
-        <v>6717630</v>
+        <v>6717644</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1205,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483850</v>
+        <v>123483916</v>
       </c>
       <c r="B7" t="n">
-        <v>95689</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,31 +1219,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461289</v>
+        <v>461192</v>
       </c>
       <c r="R7" t="n">
-        <v>6717597</v>
+        <v>6717590</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1312,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483963</v>
+        <v>123483686</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,13 +1356,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461225</v>
+        <v>461374</v>
       </c>
       <c r="R8" t="n">
-        <v>6717644</v>
+        <v>6717611</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483916</v>
+        <v>123483907</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461192</v>
+        <v>461180</v>
       </c>
       <c r="R9" t="n">
-        <v>6717590</v>
+        <v>6717581</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1524,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483865</v>
+        <v>123483933</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,39 +1537,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1576,13 +1568,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461215</v>
+        <v>461186</v>
       </c>
       <c r="R10" t="n">
-        <v>6717569</v>
+        <v>6717575</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483701</v>
+        <v>123483843</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,30 +1643,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1682,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461349</v>
+        <v>461305</v>
       </c>
       <c r="R11" t="n">
-        <v>6717583</v>
+        <v>6717564</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483953</v>
+        <v>123483701</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1788,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461210</v>
+        <v>461349</v>
       </c>
       <c r="R12" t="n">
-        <v>6717613</v>
+        <v>6717583</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483843</v>
+        <v>123483657</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,39 +1864,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1903,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461305</v>
+        <v>461361</v>
       </c>
       <c r="R13" t="n">
-        <v>6717564</v>
+        <v>6717583</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483817</v>
+        <v>123483865</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,10 +1993,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2014,10 +2010,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461318</v>
+        <v>461215</v>
       </c>
       <c r="R14" t="n">
-        <v>6717563</v>
+        <v>6717569</v>
       </c>
       <c r="S14" t="n">
         <v>75</v>
@@ -2077,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483762</v>
+        <v>123483730</v>
       </c>
       <c r="B15" t="n">
-        <v>95689</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,31 +2085,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2121,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461360</v>
+        <v>461321</v>
       </c>
       <c r="R15" t="n">
-        <v>6717558</v>
+        <v>6717630</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2184,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483794</v>
+        <v>123483953</v>
       </c>
       <c r="B16" t="n">
-        <v>95689</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,31 +2191,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2228,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461357</v>
+        <v>461210</v>
       </c>
       <c r="R16" t="n">
-        <v>6717536</v>
+        <v>6717613</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2291,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483686</v>
+        <v>123483762</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>95695</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,30 +2297,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2334,13 +2329,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461374</v>
+        <v>461360</v>
       </c>
       <c r="R17" t="n">
-        <v>6717611</v>
+        <v>6717558</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2397,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483888</v>
+        <v>123483898</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2449,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461180</v>
+        <v>461163</v>
       </c>
       <c r="R18" t="n">
-        <v>6717538</v>
+        <v>6717595</v>
       </c>
       <c r="S18" t="n">
         <v>75</v>
@@ -2512,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483693</v>
+        <v>123483735</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2555,13 +2550,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461349</v>
+        <v>461338</v>
       </c>
       <c r="R19" t="n">
-        <v>6717595</v>
+        <v>6717621</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483602</v>
+        <v>123483817</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,30 +2625,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461381</v>
+        <v>461318</v>
       </c>
       <c r="R20" t="n">
-        <v>6717608</v>
+        <v>6717563</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483942</v>
+        <v>123483640</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461218</v>
+        <v>461380</v>
       </c>
       <c r="R21" t="n">
-        <v>6717602</v>
+        <v>6717576</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483679</v>
+        <v>123483670</v>
       </c>
       <c r="B22" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461365</v>
+        <v>461373</v>
       </c>
       <c r="R22" t="n">
-        <v>6717606</v>
+        <v>6717597</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483933</v>
+        <v>123483888</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,30 +2948,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2979,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461186</v>
+        <v>461180</v>
       </c>
       <c r="R23" t="n">
-        <v>6717575</v>
+        <v>6717538</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3042,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483670</v>
+        <v>123483726</v>
       </c>
       <c r="B24" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3085,13 +3094,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461373</v>
+        <v>461329</v>
       </c>
       <c r="R24" t="n">
-        <v>6717597</v>
+        <v>6717642</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483735</v>
+        <v>123483693</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461338</v>
+        <v>461349</v>
       </c>
       <c r="R25" t="n">
-        <v>6717621</v>
+        <v>6717595</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483898</v>
+        <v>123483942</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3266,39 +3275,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461163</v>
+        <v>461218</v>
       </c>
       <c r="R26" t="n">
-        <v>6717595</v>
+        <v>6717602</v>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483850</v>
+        <v>123483640</v>
       </c>
       <c r="B2" t="n">
-        <v>95695</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461289</v>
+        <v>461380</v>
       </c>
       <c r="R2" t="n">
-        <v>6717597</v>
+        <v>6717576</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483679</v>
+        <v>123483888</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +793,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461365</v>
+        <v>461180</v>
       </c>
       <c r="R3" t="n">
-        <v>6717606</v>
+        <v>6717538</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483794</v>
+        <v>123483602</v>
       </c>
       <c r="B4" t="n">
-        <v>95695</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461357</v>
+        <v>461381</v>
       </c>
       <c r="R4" t="n">
-        <v>6717536</v>
+        <v>6717608</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483602</v>
+        <v>123483898</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,30 +1014,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461381</v>
+        <v>461163</v>
       </c>
       <c r="R5" t="n">
-        <v>6717608</v>
+        <v>6717595</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483963</v>
+        <v>123483843</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,30 +1129,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461225</v>
+        <v>461305</v>
       </c>
       <c r="R6" t="n">
-        <v>6717644</v>
+        <v>6717564</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1207,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483916</v>
+        <v>123483953</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461192</v>
+        <v>461210</v>
       </c>
       <c r="R7" t="n">
-        <v>6717590</v>
+        <v>6717613</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1313,10 +1338,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483686</v>
+        <v>123483670</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461374</v>
+        <v>461373</v>
       </c>
       <c r="R8" t="n">
-        <v>6717611</v>
+        <v>6717597</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1419,10 +1444,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483907</v>
+        <v>123483657</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,13 +1487,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461180</v>
+        <v>461361</v>
       </c>
       <c r="R9" t="n">
-        <v>6717581</v>
+        <v>6717583</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1553,7 @@
         <v>123483933</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483843</v>
+        <v>123483865</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,7 +1691,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1683,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461305</v>
+        <v>461215</v>
       </c>
       <c r="R11" t="n">
-        <v>6717564</v>
+        <v>6717569</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,10 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483701</v>
+        <v>123483735</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461349</v>
+        <v>461338</v>
       </c>
       <c r="R12" t="n">
-        <v>6717583</v>
+        <v>6717621</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483657</v>
+        <v>123483762</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>95697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,30 +1889,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1895,13 +1921,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461361</v>
+        <v>461360</v>
       </c>
       <c r="R13" t="n">
-        <v>6717583</v>
+        <v>6717558</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,10 +1984,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483865</v>
+        <v>123483686</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,39 +1996,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2010,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461215</v>
+        <v>461374</v>
       </c>
       <c r="R14" t="n">
-        <v>6717569</v>
+        <v>6717611</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483730</v>
+        <v>123483693</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2116,13 +2133,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461321</v>
+        <v>461349</v>
       </c>
       <c r="R15" t="n">
-        <v>6717630</v>
+        <v>6717595</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483953</v>
+        <v>123483907</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2222,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461210</v>
+        <v>461180</v>
       </c>
       <c r="R16" t="n">
-        <v>6717613</v>
+        <v>6717581</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2285,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483762</v>
+        <v>123483730</v>
       </c>
       <c r="B17" t="n">
-        <v>95695</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,31 +2314,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461360</v>
+        <v>461321</v>
       </c>
       <c r="R17" t="n">
-        <v>6717558</v>
+        <v>6717630</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2392,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483898</v>
+        <v>123483850</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>95697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2404,37 +2420,29 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2444,13 +2452,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461163</v>
+        <v>461289</v>
       </c>
       <c r="R18" t="n">
-        <v>6717595</v>
+        <v>6717597</v>
       </c>
       <c r="S18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2507,10 +2515,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483735</v>
+        <v>123483916</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2550,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461338</v>
+        <v>461192</v>
       </c>
       <c r="R19" t="n">
-        <v>6717621</v>
+        <v>6717590</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2616,7 +2624,7 @@
         <v>123483817</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2732,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483640</v>
+        <v>123483942</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2767,13 +2775,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461380</v>
+        <v>461218</v>
       </c>
       <c r="R21" t="n">
-        <v>6717576</v>
+        <v>6717602</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2830,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483670</v>
+        <v>123483794</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>95697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2842,30 +2850,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2873,13 +2882,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461373</v>
+        <v>461357</v>
       </c>
       <c r="R22" t="n">
-        <v>6717597</v>
+        <v>6717536</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483888</v>
+        <v>123483701</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,39 +2957,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461180</v>
+        <v>461349</v>
       </c>
       <c r="R23" t="n">
-        <v>6717538</v>
+        <v>6717583</v>
       </c>
       <c r="S23" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483726</v>
+        <v>123483679</v>
       </c>
       <c r="B24" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3094,13 +3094,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461329</v>
+        <v>461365</v>
       </c>
       <c r="R24" t="n">
-        <v>6717642</v>
+        <v>6717606</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483693</v>
+        <v>123483726</v>
       </c>
       <c r="B25" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461349</v>
+        <v>461329</v>
       </c>
       <c r="R25" t="n">
-        <v>6717595</v>
+        <v>6717642</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483942</v>
+        <v>123483963</v>
       </c>
       <c r="B26" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461218</v>
+        <v>461225</v>
       </c>
       <c r="R26" t="n">
-        <v>6717602</v>
+        <v>6717644</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483865</v>
+        <v>123483735</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,39 +1668,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1708,13 +1699,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461215</v>
+        <v>461338</v>
       </c>
       <c r="R11" t="n">
-        <v>6717569</v>
+        <v>6717621</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483735</v>
+        <v>123483865</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,30 +1774,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461338</v>
+        <v>461215</v>
       </c>
       <c r="R12" t="n">
-        <v>6717621</v>
+        <v>6717569</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483888</v>
+        <v>123483762</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>96205</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -833,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461180</v>
+        <v>461360</v>
       </c>
       <c r="R3" t="n">
-        <v>6717538</v>
+        <v>6717558</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483602</v>
+        <v>123483850</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +900,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461381</v>
+        <v>461289</v>
       </c>
       <c r="R4" t="n">
-        <v>6717608</v>
+        <v>6717597</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483898</v>
+        <v>123483916</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,39 +1007,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461163</v>
+        <v>461192</v>
       </c>
       <c r="R5" t="n">
-        <v>6717595</v>
+        <v>6717590</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1104,7 @@
         <v>123483843</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1232,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483953</v>
+        <v>123483686</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1275,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461210</v>
+        <v>461374</v>
       </c>
       <c r="R7" t="n">
-        <v>6717613</v>
+        <v>6717611</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483670</v>
+        <v>123483602</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1381,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461373</v>
+        <v>461381</v>
       </c>
       <c r="R8" t="n">
-        <v>6717597</v>
+        <v>6717608</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483657</v>
+        <v>123483888</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,30 +1440,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1487,13 +1480,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461361</v>
+        <v>461180</v>
       </c>
       <c r="R9" t="n">
-        <v>6717583</v>
+        <v>6717538</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1543,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483933</v>
+        <v>123483701</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1593,13 +1586,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461186</v>
+        <v>461349</v>
       </c>
       <c r="R10" t="n">
-        <v>6717575</v>
+        <v>6717583</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,7 +1649,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483735</v>
+        <v>123483726</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1699,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461338</v>
+        <v>461329</v>
       </c>
       <c r="R11" t="n">
-        <v>6717621</v>
+        <v>6717642</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1762,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483865</v>
+        <v>123483963</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,39 +1767,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1814,13 +1798,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461215</v>
+        <v>461225</v>
       </c>
       <c r="R12" t="n">
-        <v>6717569</v>
+        <v>6717644</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483762</v>
+        <v>123483953</v>
       </c>
       <c r="B13" t="n">
-        <v>95697</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,31 +1873,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1921,10 +1904,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461360</v>
+        <v>461210</v>
       </c>
       <c r="R13" t="n">
-        <v>6717558</v>
+        <v>6717613</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1984,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483686</v>
+        <v>123483898</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,30 +1979,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461374</v>
+        <v>461163</v>
       </c>
       <c r="R14" t="n">
-        <v>6717611</v>
+        <v>6717595</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2082,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483693</v>
+        <v>123483933</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2133,13 +2125,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461349</v>
+        <v>461186</v>
       </c>
       <c r="R15" t="n">
-        <v>6717595</v>
+        <v>6717575</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483907</v>
+        <v>123483794</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,30 +2200,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2239,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461180</v>
+        <v>461357</v>
       </c>
       <c r="R16" t="n">
-        <v>6717581</v>
+        <v>6717536</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2302,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483730</v>
+        <v>123483865</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,30 +2307,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2345,13 +2347,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461321</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6717630</v>
+        <v>6717569</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2408,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483850</v>
+        <v>123483817</v>
       </c>
       <c r="B18" t="n">
-        <v>95697</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2420,28 +2422,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2452,13 +2458,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461289</v>
+        <v>461318</v>
       </c>
       <c r="R18" t="n">
-        <v>6717597</v>
+        <v>6717563</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2515,7 +2521,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483916</v>
+        <v>123483942</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2558,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461192</v>
+        <v>461218</v>
       </c>
       <c r="R19" t="n">
-        <v>6717590</v>
+        <v>6717602</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2621,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483817</v>
+        <v>123483730</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2633,35 +2639,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2669,13 +2670,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461318</v>
+        <v>461321</v>
       </c>
       <c r="R20" t="n">
-        <v>6717563</v>
+        <v>6717630</v>
       </c>
       <c r="S20" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2733,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483942</v>
+        <v>123483679</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2775,13 +2776,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461218</v>
+        <v>461365</v>
       </c>
       <c r="R21" t="n">
-        <v>6717602</v>
+        <v>6717606</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2838,10 +2839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483794</v>
+        <v>123483735</v>
       </c>
       <c r="B22" t="n">
-        <v>95697</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2850,31 +2851,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461357</v>
+        <v>461338</v>
       </c>
       <c r="R22" t="n">
-        <v>6717536</v>
+        <v>6717621</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483701</v>
+        <v>123483657</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461349</v>
+        <v>461361</v>
       </c>
       <c r="R23" t="n">
         <v>6717583</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483679</v>
+        <v>123483670</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461365</v>
+        <v>461373</v>
       </c>
       <c r="R24" t="n">
-        <v>6717606</v>
+        <v>6717597</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483726</v>
+        <v>123483907</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461329</v>
+        <v>461180</v>
       </c>
       <c r="R25" t="n">
-        <v>6717642</v>
+        <v>6717581</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483963</v>
+        <v>123483693</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461225</v>
+        <v>461349</v>
       </c>
       <c r="R26" t="n">
-        <v>6717644</v>
+        <v>6717595</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483640</v>
+        <v>123483657</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461380</v>
+        <v>461361</v>
       </c>
       <c r="R2" t="n">
-        <v>6717576</v>
+        <v>6717583</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483762</v>
+        <v>123483916</v>
       </c>
       <c r="B3" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,31 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461360</v>
+        <v>461192</v>
       </c>
       <c r="R3" t="n">
-        <v>6717558</v>
+        <v>6717590</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483850</v>
+        <v>123483843</v>
       </c>
       <c r="B4" t="n">
-        <v>96205</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,29 +899,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -932,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461289</v>
+        <v>461305</v>
       </c>
       <c r="R4" t="n">
-        <v>6717597</v>
+        <v>6717564</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -995,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483916</v>
+        <v>123483762</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,30 +1014,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461192</v>
+        <v>461360</v>
       </c>
       <c r="R5" t="n">
-        <v>6717590</v>
+        <v>6717558</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1101,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483843</v>
+        <v>123483850</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,37 +1121,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461305</v>
+        <v>461289</v>
       </c>
       <c r="R6" t="n">
-        <v>6717564</v>
+        <v>6717597</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483686</v>
+        <v>123483933</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461374</v>
+        <v>461186</v>
       </c>
       <c r="R7" t="n">
-        <v>6717611</v>
+        <v>6717575</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483602</v>
+        <v>123483693</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461381</v>
+        <v>461349</v>
       </c>
       <c r="R8" t="n">
-        <v>6717608</v>
+        <v>6717595</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483888</v>
+        <v>123483794</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,37 +1440,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1480,13 +1472,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461180</v>
+        <v>461357</v>
       </c>
       <c r="R9" t="n">
-        <v>6717538</v>
+        <v>6717536</v>
       </c>
       <c r="S9" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1535,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483701</v>
+        <v>123483686</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1586,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461349</v>
+        <v>461374</v>
       </c>
       <c r="R10" t="n">
-        <v>6717583</v>
+        <v>6717611</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1649,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483726</v>
+        <v>123483865</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,30 +1653,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1692,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461329</v>
+        <v>461215</v>
       </c>
       <c r="R11" t="n">
-        <v>6717642</v>
+        <v>6717569</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483963</v>
+        <v>123483817</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1767,30 +1768,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1798,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461225</v>
+        <v>461318</v>
       </c>
       <c r="R12" t="n">
-        <v>6717644</v>
+        <v>6717563</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1861,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483953</v>
+        <v>123483640</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1904,13 +1910,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461210</v>
+        <v>461380</v>
       </c>
       <c r="R13" t="n">
-        <v>6717613</v>
+        <v>6717576</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483898</v>
+        <v>123483735</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,39 +1985,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,13 +2016,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461163</v>
+        <v>461338</v>
       </c>
       <c r="R14" t="n">
-        <v>6717595</v>
+        <v>6717621</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2082,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483933</v>
+        <v>123483701</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2125,13 +2122,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461186</v>
+        <v>461349</v>
       </c>
       <c r="R15" t="n">
-        <v>6717575</v>
+        <v>6717583</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483794</v>
+        <v>123483602</v>
       </c>
       <c r="B16" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,31 +2197,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2232,13 +2228,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461357</v>
+        <v>461381</v>
       </c>
       <c r="R16" t="n">
-        <v>6717536</v>
+        <v>6717608</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483865</v>
+        <v>123483730</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,39 +2303,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2347,13 +2334,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461321</v>
       </c>
       <c r="R17" t="n">
-        <v>6717569</v>
+        <v>6717630</v>
       </c>
       <c r="S17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483817</v>
+        <v>123483907</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,35 +2409,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2458,13 +2440,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461318</v>
+        <v>461180</v>
       </c>
       <c r="R18" t="n">
-        <v>6717563</v>
+        <v>6717581</v>
       </c>
       <c r="S18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2521,7 +2503,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483942</v>
+        <v>123483726</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2564,10 +2546,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461218</v>
+        <v>461329</v>
       </c>
       <c r="R19" t="n">
-        <v>6717602</v>
+        <v>6717642</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2627,7 +2609,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483730</v>
+        <v>123483670</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2670,13 +2652,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461321</v>
+        <v>461373</v>
       </c>
       <c r="R20" t="n">
-        <v>6717630</v>
+        <v>6717597</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483679</v>
+        <v>123483888</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,30 +2727,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2776,13 +2767,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461365</v>
+        <v>461180</v>
       </c>
       <c r="R21" t="n">
-        <v>6717606</v>
+        <v>6717538</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2839,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483735</v>
+        <v>123483898</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,30 +2842,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461338</v>
+        <v>461163</v>
       </c>
       <c r="R22" t="n">
-        <v>6717621</v>
+        <v>6717595</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483657</v>
+        <v>123483963</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2988,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461361</v>
+        <v>461225</v>
       </c>
       <c r="R23" t="n">
-        <v>6717583</v>
+        <v>6717644</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483670</v>
+        <v>123483942</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3094,13 +3094,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461373</v>
+        <v>461218</v>
       </c>
       <c r="R24" t="n">
-        <v>6717597</v>
+        <v>6717602</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483907</v>
+        <v>123483953</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461180</v>
+        <v>461210</v>
       </c>
       <c r="R25" t="n">
-        <v>6717581</v>
+        <v>6717613</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483693</v>
+        <v>123483679</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461349</v>
+        <v>461365</v>
       </c>
       <c r="R26" t="n">
-        <v>6717595</v>
+        <v>6717606</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483657</v>
+        <v>123483686</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461361</v>
+        <v>461374</v>
       </c>
       <c r="R2" t="n">
-        <v>6717583</v>
+        <v>6717611</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483916</v>
+        <v>123483730</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461192</v>
+        <v>461321</v>
       </c>
       <c r="R3" t="n">
-        <v>6717590</v>
+        <v>6717630</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483843</v>
+        <v>123483726</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461305</v>
+        <v>461329</v>
       </c>
       <c r="R4" t="n">
-        <v>6717564</v>
+        <v>6717642</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483762</v>
+        <v>123483602</v>
       </c>
       <c r="B5" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,31 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461360</v>
+        <v>461381</v>
       </c>
       <c r="R5" t="n">
-        <v>6717558</v>
+        <v>6717608</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483850</v>
+        <v>123483701</v>
       </c>
       <c r="B6" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,31 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461289</v>
+        <v>461349</v>
       </c>
       <c r="R6" t="n">
-        <v>6717597</v>
+        <v>6717583</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483933</v>
+        <v>123483916</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1259,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461186</v>
+        <v>461192</v>
       </c>
       <c r="R7" t="n">
-        <v>6717575</v>
+        <v>6717590</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1322,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483693</v>
+        <v>123483640</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1365,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461349</v>
+        <v>461380</v>
       </c>
       <c r="R8" t="n">
-        <v>6717595</v>
+        <v>6717576</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483794</v>
+        <v>123483843</v>
       </c>
       <c r="B9" t="n">
-        <v>96205</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,29 +1429,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1472,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461357</v>
+        <v>461305</v>
       </c>
       <c r="R9" t="n">
-        <v>6717536</v>
+        <v>6717564</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1535,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483686</v>
+        <v>123483865</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,30 +1544,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,13 +1584,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461374</v>
+        <v>461215</v>
       </c>
       <c r="R10" t="n">
-        <v>6717611</v>
+        <v>6717569</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483865</v>
+        <v>123483693</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,39 +1659,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,13 +1690,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461215</v>
+        <v>461349</v>
       </c>
       <c r="R11" t="n">
-        <v>6717569</v>
+        <v>6717595</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1756,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483817</v>
+        <v>123483794</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,32 +1765,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1804,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461318</v>
+        <v>461357</v>
       </c>
       <c r="R12" t="n">
-        <v>6717563</v>
+        <v>6717536</v>
       </c>
       <c r="S12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483640</v>
+        <v>123483898</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,30 +1872,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,13 +1912,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461380</v>
+        <v>461163</v>
       </c>
       <c r="R13" t="n">
-        <v>6717576</v>
+        <v>6717595</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483735</v>
+        <v>123483888</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,30 +1987,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461338</v>
+        <v>461180</v>
       </c>
       <c r="R14" t="n">
-        <v>6717621</v>
+        <v>6717538</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2079,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483701</v>
+        <v>123483817</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,30 +2102,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2122,13 +2138,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461349</v>
+        <v>461318</v>
       </c>
       <c r="R15" t="n">
-        <v>6717583</v>
+        <v>6717563</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2185,7 +2201,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483602</v>
+        <v>123483953</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2228,13 +2244,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461381</v>
+        <v>461210</v>
       </c>
       <c r="R16" t="n">
-        <v>6717608</v>
+        <v>6717613</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2291,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483730</v>
+        <v>123483679</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2334,13 +2350,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461321</v>
+        <v>461365</v>
       </c>
       <c r="R17" t="n">
-        <v>6717630</v>
+        <v>6717606</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2397,7 +2413,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483907</v>
+        <v>123483657</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2440,13 +2456,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461180</v>
+        <v>461361</v>
       </c>
       <c r="R18" t="n">
-        <v>6717581</v>
+        <v>6717583</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483726</v>
+        <v>123483963</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2546,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461329</v>
+        <v>461225</v>
       </c>
       <c r="R19" t="n">
-        <v>6717642</v>
+        <v>6717644</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2609,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483670</v>
+        <v>123483907</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2652,13 +2668,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461373</v>
+        <v>461180</v>
       </c>
       <c r="R20" t="n">
-        <v>6717597</v>
+        <v>6717581</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2715,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483888</v>
+        <v>123483735</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,39 +2743,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2767,13 +2774,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461180</v>
+        <v>461338</v>
       </c>
       <c r="R21" t="n">
-        <v>6717538</v>
+        <v>6717621</v>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2830,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483898</v>
+        <v>123483762</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2842,37 +2849,29 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2882,13 +2881,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461163</v>
+        <v>461360</v>
       </c>
       <c r="R22" t="n">
-        <v>6717595</v>
+        <v>6717558</v>
       </c>
       <c r="S22" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2945,7 +2944,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483963</v>
+        <v>123483933</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2988,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461225</v>
+        <v>461186</v>
       </c>
       <c r="R23" t="n">
-        <v>6717644</v>
+        <v>6717575</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3051,10 +3050,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483942</v>
+        <v>123483850</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,30 +3062,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461218</v>
+        <v>461289</v>
       </c>
       <c r="R24" t="n">
-        <v>6717602</v>
+        <v>6717597</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483953</v>
+        <v>123483670</v>
       </c>
       <c r="B25" t="n">
         <v>78788</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461210</v>
+        <v>461373</v>
       </c>
       <c r="R25" t="n">
-        <v>6717613</v>
+        <v>6717597</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483679</v>
+        <v>123483942</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461365</v>
+        <v>461218</v>
       </c>
       <c r="R26" t="n">
-        <v>6717606</v>
+        <v>6717602</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483686</v>
+        <v>123483794</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461374</v>
+        <v>461357</v>
       </c>
       <c r="R2" t="n">
-        <v>6717611</v>
+        <v>6717536</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483730</v>
+        <v>123483726</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461321</v>
+        <v>461329</v>
       </c>
       <c r="R3" t="n">
-        <v>6717630</v>
+        <v>6717642</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483726</v>
+        <v>123483898</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +900,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461329</v>
+        <v>461163</v>
       </c>
       <c r="R4" t="n">
-        <v>6717642</v>
+        <v>6717595</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483602</v>
+        <v>123483850</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,30 +1015,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461381</v>
+        <v>461289</v>
       </c>
       <c r="R5" t="n">
-        <v>6717608</v>
+        <v>6717597</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483701</v>
+        <v>123483916</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1142,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461349</v>
+        <v>461192</v>
       </c>
       <c r="R6" t="n">
-        <v>6717583</v>
+        <v>6717590</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,7 +1216,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483916</v>
+        <v>123483701</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1248,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461192</v>
+        <v>461349</v>
       </c>
       <c r="R7" t="n">
-        <v>6717590</v>
+        <v>6717583</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483640</v>
+        <v>123483730</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1354,13 +1365,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461380</v>
+        <v>461321</v>
       </c>
       <c r="R8" t="n">
-        <v>6717576</v>
+        <v>6717630</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483843</v>
+        <v>123483907</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,39 +1440,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1469,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461305</v>
+        <v>461180</v>
       </c>
       <c r="R9" t="n">
-        <v>6717564</v>
+        <v>6717581</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483865</v>
+        <v>123483735</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,39 +1546,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1584,13 +1577,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461215</v>
+        <v>461338</v>
       </c>
       <c r="R10" t="n">
-        <v>6717569</v>
+        <v>6717621</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483693</v>
+        <v>123483933</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1690,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461349</v>
+        <v>461186</v>
       </c>
       <c r="R11" t="n">
-        <v>6717595</v>
+        <v>6717575</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483794</v>
+        <v>123483640</v>
       </c>
       <c r="B12" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,31 +1758,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1797,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461357</v>
+        <v>461380</v>
       </c>
       <c r="R12" t="n">
-        <v>6717536</v>
+        <v>6717576</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483898</v>
+        <v>123483602</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,39 +1864,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,13 +1895,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461163</v>
+        <v>461381</v>
       </c>
       <c r="R13" t="n">
-        <v>6717595</v>
+        <v>6717608</v>
       </c>
       <c r="S13" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1975,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483888</v>
+        <v>123483762</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,37 +1970,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2027,13 +2002,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461180</v>
+        <v>461360</v>
       </c>
       <c r="R14" t="n">
-        <v>6717538</v>
+        <v>6717558</v>
       </c>
       <c r="S14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483817</v>
+        <v>123483686</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,35 +2077,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2138,13 +2108,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461318</v>
+        <v>461374</v>
       </c>
       <c r="R15" t="n">
-        <v>6717563</v>
+        <v>6717611</v>
       </c>
       <c r="S15" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,7 +2171,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483953</v>
+        <v>123483693</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2244,13 +2214,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461210</v>
+        <v>461349</v>
       </c>
       <c r="R16" t="n">
-        <v>6717613</v>
+        <v>6717595</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2307,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483679</v>
+        <v>123483865</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2319,30 +2289,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2350,13 +2329,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461365</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6717606</v>
+        <v>6717569</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2519,7 +2498,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483963</v>
+        <v>123483679</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2562,13 +2541,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461225</v>
+        <v>461365</v>
       </c>
       <c r="R19" t="n">
-        <v>6717644</v>
+        <v>6717606</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483907</v>
+        <v>123483843</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,30 +2616,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2668,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461180</v>
+        <v>461305</v>
       </c>
       <c r="R20" t="n">
-        <v>6717581</v>
+        <v>6717564</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2731,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483735</v>
+        <v>123483963</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2774,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461338</v>
+        <v>461225</v>
       </c>
       <c r="R21" t="n">
-        <v>6717621</v>
+        <v>6717644</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2837,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483762</v>
+        <v>123483953</v>
       </c>
       <c r="B22" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2849,31 +2837,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2881,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461360</v>
+        <v>461210</v>
       </c>
       <c r="R22" t="n">
-        <v>6717558</v>
+        <v>6717613</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2944,7 +2931,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483933</v>
+        <v>123483670</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2987,13 +2974,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461186</v>
+        <v>461373</v>
       </c>
       <c r="R23" t="n">
-        <v>6717575</v>
+        <v>6717597</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483850</v>
+        <v>123483888</v>
       </c>
       <c r="B24" t="n">
-        <v>96205</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3062,29 +3049,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3094,13 +3089,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461289</v>
+        <v>461180</v>
       </c>
       <c r="R24" t="n">
-        <v>6717597</v>
+        <v>6717538</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,10 +3152,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483670</v>
+        <v>123483817</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3169,30 +3164,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461373</v>
+        <v>461318</v>
       </c>
       <c r="R25" t="n">
-        <v>6717597</v>
+        <v>6717563</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483898</v>
+        <v>123483850</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>96205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -940,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461163</v>
+        <v>461289</v>
       </c>
       <c r="R4" t="n">
-        <v>6717595</v>
+        <v>6717597</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483850</v>
+        <v>123483898</v>
       </c>
       <c r="B5" t="n">
-        <v>96205</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,29 +1007,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461289</v>
+        <v>461163</v>
       </c>
       <c r="R5" t="n">
-        <v>6717597</v>
+        <v>6717595</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483693</v>
+        <v>123483865</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,30 +2183,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2214,13 +2223,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461349</v>
+        <v>461215</v>
       </c>
       <c r="R16" t="n">
-        <v>6717595</v>
+        <v>6717569</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483865</v>
+        <v>123483693</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,39 +2298,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461349</v>
       </c>
       <c r="R17" t="n">
-        <v>6717569</v>
+        <v>6717595</v>
       </c>
       <c r="S17" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483888</v>
+        <v>123483942</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3049,39 +3049,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3089,13 +3080,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461180</v>
+        <v>461218</v>
       </c>
       <c r="R24" t="n">
-        <v>6717538</v>
+        <v>6717602</v>
       </c>
       <c r="S24" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3143,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483817</v>
+        <v>123483888</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3187,10 +3178,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3200,10 +3195,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461318</v>
+        <v>461180</v>
       </c>
       <c r="R25" t="n">
-        <v>6717563</v>
+        <v>6717538</v>
       </c>
       <c r="S25" t="n">
         <v>75</v>
@@ -3263,10 +3258,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483942</v>
+        <v>123483817</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3275,30 +3270,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461218</v>
+        <v>461318</v>
       </c>
       <c r="R26" t="n">
-        <v>6717602</v>
+        <v>6717563</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483794</v>
+        <v>123483657</v>
       </c>
       <c r="B2" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461357</v>
+        <v>461361</v>
       </c>
       <c r="R2" t="n">
-        <v>6717536</v>
+        <v>6717583</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123483726</v>
+        <v>123483953</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461329</v>
+        <v>461210</v>
       </c>
       <c r="R3" t="n">
-        <v>6717642</v>
+        <v>6717613</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -888,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483850</v>
+        <v>123483933</v>
       </c>
       <c r="B4" t="n">
-        <v>96205</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461289</v>
+        <v>461186</v>
       </c>
       <c r="R4" t="n">
-        <v>6717597</v>
+        <v>6717575</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -995,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483898</v>
+        <v>123483817</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1030,14 +1028,10 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1047,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461163</v>
+        <v>461318</v>
       </c>
       <c r="R5" t="n">
-        <v>6717595</v>
+        <v>6717563</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1110,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483916</v>
+        <v>123483686</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1153,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461192</v>
+        <v>461374</v>
       </c>
       <c r="R6" t="n">
-        <v>6717590</v>
+        <v>6717611</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483701</v>
+        <v>123483602</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1259,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461349</v>
+        <v>461381</v>
       </c>
       <c r="R7" t="n">
-        <v>6717583</v>
+        <v>6717608</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483730</v>
+        <v>123483640</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1365,13 +1359,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461321</v>
+        <v>461380</v>
       </c>
       <c r="R8" t="n">
-        <v>6717630</v>
+        <v>6717576</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483907</v>
+        <v>123483701</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1471,13 +1465,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461180</v>
+        <v>461349</v>
       </c>
       <c r="R9" t="n">
-        <v>6717581</v>
+        <v>6717583</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1528,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483735</v>
+        <v>123483679</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1577,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461338</v>
+        <v>461365</v>
       </c>
       <c r="R10" t="n">
-        <v>6717621</v>
+        <v>6717606</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,7 +1634,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483933</v>
+        <v>123483670</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1683,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461186</v>
+        <v>461373</v>
       </c>
       <c r="R11" t="n">
-        <v>6717575</v>
+        <v>6717597</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1746,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483640</v>
+        <v>123483794</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,30 +1752,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1789,13 +1784,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461380</v>
+        <v>461357</v>
       </c>
       <c r="R12" t="n">
-        <v>6717576</v>
+        <v>6717536</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483602</v>
+        <v>123483762</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,30 +1859,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1895,13 +1891,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461381</v>
+        <v>461360</v>
       </c>
       <c r="R13" t="n">
-        <v>6717608</v>
+        <v>6717558</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483762</v>
+        <v>123483898</v>
       </c>
       <c r="B14" t="n">
-        <v>96205</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1970,29 +1966,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -2002,13 +2006,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461360</v>
+        <v>461163</v>
       </c>
       <c r="R14" t="n">
-        <v>6717558</v>
+        <v>6717595</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2065,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483686</v>
+        <v>123483907</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2108,13 +2112,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461374</v>
+        <v>461180</v>
       </c>
       <c r="R15" t="n">
-        <v>6717611</v>
+        <v>6717581</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483693</v>
+        <v>123483850</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>96205</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,30 +2302,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2329,13 +2334,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461349</v>
+        <v>461289</v>
       </c>
       <c r="R17" t="n">
-        <v>6717595</v>
+        <v>6717597</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2397,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483657</v>
+        <v>123483735</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2435,13 +2440,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461361</v>
+        <v>461338</v>
       </c>
       <c r="R18" t="n">
-        <v>6717583</v>
+        <v>6717621</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483679</v>
+        <v>123483888</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2510,30 +2515,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2541,13 +2555,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461365</v>
+        <v>461180</v>
       </c>
       <c r="R19" t="n">
-        <v>6717606</v>
+        <v>6717538</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2604,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483843</v>
+        <v>123483693</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,39 +2630,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2656,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461305</v>
+        <v>461349</v>
       </c>
       <c r="R20" t="n">
-        <v>6717564</v>
+        <v>6717595</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2719,7 +2724,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483963</v>
+        <v>123483916</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461225</v>
+        <v>461192</v>
       </c>
       <c r="R21" t="n">
-        <v>6717644</v>
+        <v>6717590</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2825,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483953</v>
+        <v>123483843</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,30 +2842,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2868,10 +2882,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461210</v>
+        <v>461305</v>
       </c>
       <c r="R22" t="n">
-        <v>6717613</v>
+        <v>6717564</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2931,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483670</v>
+        <v>123483963</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -2974,13 +2988,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461373</v>
+        <v>461225</v>
       </c>
       <c r="R23" t="n">
-        <v>6717597</v>
+        <v>6717644</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3143,10 +3157,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483888</v>
+        <v>123483730</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3155,39 +3169,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3195,13 +3200,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461180</v>
+        <v>461321</v>
       </c>
       <c r="R25" t="n">
-        <v>6717538</v>
+        <v>6717630</v>
       </c>
       <c r="S25" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3258,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123483817</v>
+        <v>123483726</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3270,35 +3275,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461318</v>
+        <v>461329</v>
       </c>
       <c r="R26" t="n">
-        <v>6717563</v>
+        <v>6717642</v>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123483907</v>
+        <v>123483762</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461180</v>
+        <v>461360</v>
       </c>
       <c r="R2" t="n">
-        <v>6717581</v>
+        <v>6717558</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -784,12 +780,7 @@
         <v>123483794</v>
       </c>
       <c r="B3" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,42 +879,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123483730</v>
+        <v>123483850</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461321</v>
+        <v>461289</v>
       </c>
       <c r="R4" t="n">
-        <v>6717630</v>
+        <v>6717597</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -994,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123483942</v>
+        <v>123483602</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1037,13 +1019,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461218</v>
+        <v>461381</v>
       </c>
       <c r="R5" t="n">
-        <v>6717602</v>
+        <v>6717608</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123483817</v>
+        <v>123483640</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,31 +1093,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,13 +1120,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461318</v>
+        <v>461380</v>
       </c>
       <c r="R6" t="n">
-        <v>6717563</v>
+        <v>6717576</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,43 +1183,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123483762</v>
+        <v>123483657</v>
       </c>
       <c r="B7" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,13 +1221,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461360</v>
+        <v>461361</v>
       </c>
       <c r="R7" t="n">
-        <v>6717558</v>
+        <v>6717583</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,15 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123483898</v>
+        <v>123483670</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,35 +1295,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,13 +1322,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461163</v>
+        <v>461373</v>
       </c>
       <c r="R8" t="n">
-        <v>6717595</v>
+        <v>6717597</v>
       </c>
       <c r="S8" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,19 +1385,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123483602</v>
+        <v>123483679</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1476,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461381</v>
+        <v>461365</v>
       </c>
       <c r="R9" t="n">
-        <v>6717608</v>
+        <v>6717606</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,19 +1486,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123483693</v>
+        <v>123483686</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1582,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461349</v>
+        <v>461374</v>
       </c>
       <c r="R10" t="n">
-        <v>6717595</v>
+        <v>6717611</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,19 +1587,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123483726</v>
+        <v>123483693</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1688,13 +1625,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461329</v>
+        <v>461349</v>
       </c>
       <c r="R11" t="n">
-        <v>6717642</v>
+        <v>6717595</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1751,19 +1688,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123483933</v>
+        <v>123483701</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1794,13 +1726,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461186</v>
+        <v>461349</v>
       </c>
       <c r="R12" t="n">
-        <v>6717575</v>
+        <v>6717583</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,19 +1789,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123483953</v>
+        <v>123483726</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1900,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461210</v>
+        <v>461329</v>
       </c>
       <c r="R13" t="n">
-        <v>6717613</v>
+        <v>6717642</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1963,19 +1890,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123483916</v>
+        <v>123483730</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2006,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461192</v>
+        <v>461321</v>
       </c>
       <c r="R14" t="n">
-        <v>6717590</v>
+        <v>6717630</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2069,15 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123483888</v>
+        <v>123483735</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,35 +2002,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2121,13 +2029,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461180</v>
+        <v>461338</v>
       </c>
       <c r="R15" t="n">
-        <v>6717538</v>
+        <v>6717621</v>
       </c>
       <c r="S15" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,19 +2092,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123483657</v>
+        <v>123483907</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2227,13 +2130,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461361</v>
+        <v>461180</v>
       </c>
       <c r="R16" t="n">
-        <v>6717583</v>
+        <v>6717581</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2290,19 +2193,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123483701</v>
+        <v>123483916</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2333,13 +2231,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461349</v>
+        <v>461192</v>
       </c>
       <c r="R17" t="n">
-        <v>6717583</v>
+        <v>6717590</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,19 +2294,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123483735</v>
+        <v>123483933</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2439,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461338</v>
+        <v>461186</v>
       </c>
       <c r="R18" t="n">
-        <v>6717621</v>
+        <v>6717575</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2502,43 +2395,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123483850</v>
+        <v>123483942</v>
       </c>
       <c r="B19" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2546,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461289</v>
+        <v>461218</v>
       </c>
       <c r="R19" t="n">
-        <v>6717597</v>
+        <v>6717602</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2609,15 +2496,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123483865</v>
+        <v>123483953</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,35 +2507,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2661,13 +2534,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461215</v>
+        <v>461210</v>
       </c>
       <c r="R20" t="n">
-        <v>6717569</v>
+        <v>6717613</v>
       </c>
       <c r="S20" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2724,19 +2597,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123483686</v>
+        <v>123483963</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2767,13 +2635,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461374</v>
+        <v>461225</v>
       </c>
       <c r="R21" t="n">
-        <v>6717611</v>
+        <v>6717644</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2830,42 +2698,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123483963</v>
+        <v>123483817</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2873,13 +2741,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461225</v>
+        <v>461318</v>
       </c>
       <c r="R22" t="n">
-        <v>6717644</v>
+        <v>6717563</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2936,42 +2804,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123483679</v>
+        <v>123483843</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2979,13 +2851,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461365</v>
+        <v>461305</v>
       </c>
       <c r="R23" t="n">
-        <v>6717606</v>
+        <v>6717564</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3042,42 +2914,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123483640</v>
+        <v>123483888</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3085,13 +2961,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461380</v>
+        <v>461180</v>
       </c>
       <c r="R24" t="n">
-        <v>6717576</v>
+        <v>6717538</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3148,42 +3024,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123483670</v>
+        <v>123483898</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3191,13 +3071,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461373</v>
+        <v>461163</v>
       </c>
       <c r="R25" t="n">
-        <v>6717597</v>
+        <v>6717595</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3251,121 +3131,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>123483843</v>
-      </c>
-      <c r="B26" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Norr Rälgen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>461305</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6717564</v>
-      </c>
-      <c r="S26" t="n">
-        <v>50</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Vansbro</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Järna</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11433-2025 artfynd.xlsx
+++ b/artfynd/A 11433-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483640</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483657</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483670</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483679</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483686</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483693</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483701</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483726</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483730</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483735</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483907</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,6 +2371,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2392,6 +2477,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483933</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2493,6 +2583,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483942</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2594,6 +2689,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483953</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483963</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2801,6 +2906,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483817</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3021,6 +3136,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3131,8 +3251,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>